--- a/backend/elderlycare-common/src/main/resources/excel_model/NursingItem.xlsx
+++ b/backend/elderlycare-common/src/main/resources/excel_model/NursingItem.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,6 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,11 +481,6 @@
           <t>说明</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>操作</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -514,11 +508,6 @@
           <t>description</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>operation</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -544,11 +533,6 @@
           <t>协助洗漱、整理床铺</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -574,11 +558,6 @@
           <t>预防褥疮</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -602,11 +581,6 @@
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>肢体功能恢复训练</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>编辑</t>
         </is>
       </c>
     </row>
